--- a/MBD/ExportData/ExportInterface.xlsx
+++ b/MBD/ExportData/ExportInterface.xlsx
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="11548" uniqueCount="700">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="19086" uniqueCount="700">
   <si>
     <t>Subsystem Number</t>
   </si>
@@ -2684,9 +2684,9 @@
     <col min="3" max="3" width="23.4609375" customWidth="true"/>
     <col min="4" max="4" width="6.765625" customWidth="true"/>
     <col min="5" max="5" width="9.3046875" customWidth="true"/>
-    <col min="6" max="6" width="4.69140625" customWidth="true"/>
+    <col min="6" max="6" width="6.07421875" customWidth="true"/>
     <col min="7" max="7" width="6.4609375" customWidth="true"/>
-    <col min="8" max="8" width="28.23046875" customWidth="true"/>
+    <col min="8" max="8" width="35.84375" customWidth="true"/>
     <col min="9" max="9" width="12" customWidth="true"/>
     <col min="10" max="10" width="14.23046875" customWidth="true"/>
   </cols>
@@ -2772,12 +2772,14 @@
         <v>16</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>52</v>
+        <v>290</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="H3" s="0"/>
+        <v>295</v>
+      </c>
+      <c r="H3" s="0" t="s">
+        <v>310</v>
+      </c>
       <c r="I3" s="0" t="s">
         <v>79</v>
       </c>
@@ -2802,12 +2804,14 @@
         <v>16</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="H4" s="0"/>
+        <v>13</v>
+      </c>
+      <c r="H4" s="0" t="s">
+        <v>23</v>
+      </c>
       <c r="I4" s="0" t="s">
         <v>32</v>
       </c>
@@ -11862,10 +11866,10 @@
         <v>16</v>
       </c>
       <c r="F55" s="0" t="s">
-        <v>493</v>
+        <v>527</v>
       </c>
       <c r="G55" s="0" t="s">
-        <v>495</v>
+        <v>415</v>
       </c>
       <c r="H55" s="0" t="s">
         <v>508</v>
@@ -16013,10 +16017,10 @@
         <v>16</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>493</v>
+        <v>527</v>
       </c>
       <c r="G16" s="0" t="s">
-        <v>495</v>
+        <v>415</v>
       </c>
       <c r="H16" s="0" t="s">
         <v>508</v>
@@ -16708,23 +16712,21 @@
         <v>4</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>698</v>
+        <v>686</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>27</v>
+        <v>687</v>
       </c>
       <c r="E38" s="0" t="s">
         <v>16</v>
       </c>
       <c r="F38" s="0" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="G38" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="H38" s="0" t="s">
-        <v>699</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="H38" s="0"/>
       <c r="I38" s="0" t="s">
         <v>203</v>
       </c>
@@ -19867,7 +19869,7 @@
     <col min="5" max="5" width="9.3046875" customWidth="true"/>
     <col min="6" max="6" width="4.69140625" customWidth="true"/>
     <col min="7" max="7" width="11.4609375" customWidth="true"/>
-    <col min="8" max="8" width="47.61328125" customWidth="true"/>
+    <col min="8" max="8" width="72.765625" customWidth="true"/>
     <col min="9" max="9" width="12" customWidth="true"/>
     <col min="10" max="10" width="14.23046875" customWidth="true"/>
   </cols>
@@ -20212,7 +20214,7 @@
         <v>36</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D12" s="0" t="s">
         <v>27</v>
@@ -20242,7 +20244,7 @@
         <v>36</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>154</v>
+        <v>590</v>
       </c>
       <c r="D13" s="0" t="s">
         <v>27</v>
@@ -20272,10 +20274,10 @@
         <v>36</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>590</v>
+        <v>135</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="E14" s="0" t="s">
         <v>16</v>
@@ -20288,7 +20290,7 @@
       </c>
       <c r="H14" s="0"/>
       <c r="I14" s="0" t="s">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="J14" s="0" t="s">
         <v>204</v>
@@ -20302,7 +20304,7 @@
         <v>36</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>135</v>
+        <v>97</v>
       </c>
       <c r="D15" s="0" t="s">
         <v>57</v>
@@ -20318,7 +20320,7 @@
       </c>
       <c r="H15" s="0"/>
       <c r="I15" s="0" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="J15" s="0" t="s">
         <v>204</v>
@@ -20332,7 +20334,7 @@
         <v>36</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D16" s="0" t="s">
         <v>57</v>
@@ -20362,10 +20364,10 @@
         <v>36</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>98</v>
+        <v>136</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="E17" s="0" t="s">
         <v>16</v>
@@ -20378,7 +20380,7 @@
       </c>
       <c r="H17" s="0"/>
       <c r="I17" s="0" t="s">
-        <v>108</v>
+        <v>203</v>
       </c>
       <c r="J17" s="0" t="s">
         <v>204</v>
@@ -20392,7 +20394,7 @@
         <v>36</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>136</v>
+        <v>600</v>
       </c>
       <c r="D18" s="0" t="s">
         <v>27</v>
@@ -20401,14 +20403,16 @@
         <v>16</v>
       </c>
       <c r="F18" s="0" t="s">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="G18" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="H18" s="0"/>
+        <v>11</v>
+      </c>
+      <c r="H18" s="0" t="s">
+        <v>554</v>
+      </c>
       <c r="I18" s="0" t="s">
-        <v>203</v>
+        <v>564</v>
       </c>
       <c r="J18" s="0" t="s">
         <v>204</v>
